--- a/daily_matches/job_matches_2026-08-07.xlsx
+++ b/daily_matches/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RAG, S3, EC2, FastAPI, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b179b1cd108b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=0a79b4f16db1d96c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Junior Data Engineer (GCP Cloud Migrations)</t>
+          <t>AI Full stack Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, AWS SageMaker, GCP Vertex AI, Azure ML, Redshift, BigQuery, Dataflow, Apache Airflow, Git</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Pinecone, ChromaDB, Prompt Engineering, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221a082ea5ba73e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8a26a0d3e920401c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer | AI Agents | Python | F2F Interview in NJ</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tms Llc</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, FAISS, Pinecone, ChromaDB, Prompt Engineering, FastAPI, Docker</t>
+          <t>TensorFlow, PyTorch, XGBoost, Data Lake, MLflow, CI/CD, Git, Databricks, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3668b042918b2d60</t>
+          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, NoSQL</t>
+          <t>TensorFlow, PyTorch, XGBoost, Data Lake, MLflow, CI/CD, Git, Databricks, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
+          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cavnue</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Kafka</t>
+          <t>Data Scientist, RAG, S3, BigQuery, Kinesis, Snowflake, Databricks, BigQuery, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ebda82ef06209d</t>
+          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Specialist, AI Engineer</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Entegris</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bedford, MA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, BigQuery, Dataflow, AKS, CI/CD, Terraform, Git</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26996de4972347a2</t>
+          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Databricks, MongoDB, Python</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MACHINE LEARNING ENGINEER II (REMOTE)</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, BigQuery, CI/CD, Git, BigQuery, Python</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60fb950ef712ad69</t>
+          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>L.E.K. Consulting</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Azure ML, Kubernetes, CI/CD, Git, Python</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9994e39082a0a354</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Software Engineer I - Backend</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Ookla</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Kinesis, Docker, Kubernetes, CI/CD, Databricks</t>
+          <t>RAG, S3, Athena, Redshift, Docker, CI/CD, Git, Redshift, MySQL, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
+          <t>https://www.indeed.com/viewjob?jk=364f445832a88e5e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Full-Stack Developer - Senior Software Engineer</t>
+          <t>Jr Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, Docker, CI/CD, Git, PostgreSQL, MySQL, SQL</t>
+          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Keras, Git, Tableau, Power BI, Matplotlib, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c820a1b6b15a1e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Software Engineer II</t>
+          <t>Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, Glue, Redshift, BigQuery, Snowflake, BigQuery, Redshift, MySQL, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb85e1999b2bc25c</t>
+          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Overseas Contractor</t>
+          <t>Data Engineer (Databricks/AWS)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, LLaMA, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Kafka</t>
+          <t>RAG, S3, Glue, Athena, Git, Databricks, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb358e064e9b104</t>
+          <t>https://www.indeed.com/viewjob?jk=de00d1a1e6d38ed7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer II</t>
+          <t>Sr. Engineer, AI Platform Engineering</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IceKredit</t>
+          <t>Petco</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LangChain, S3, EC2, FastAPI, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
+          <t>https://www.indeed.com/viewjob?jk=60da51423ca57a2c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS Full-Stack Developer - Senior Software Engineer</t>
+          <t>Software Applications Developer/Programmer III - AI/ML</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Texas A&amp;M University Corpus Christi</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Corpus Christi, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, Docker, CI/CD, Git, PostgreSQL, MySQL, SQL</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee66bd830835f06</t>
+          <t>https://www.indeed.com/viewjob?jk=5176fb526518b30d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Tableau, Power BI, Python, SQL, R</t>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad9b7febafc66a63</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Sr Data Analyst - Digital and Ecommerce (Experimentation, Math/Stats, A/B testing, ML)(Remote Or Hybrid)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Snowflake, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Git, Hadoop, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785c8caf68e944db</t>
+          <t>https://www.indeed.com/viewjob?jk=705473a3f129b496</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Data Engineer Consultant - Remote</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, CI/CD, Git, Snowflake, Databricks, Redshift, Kafka, Python, SQL, R</t>
+          <t>RAG, S3, Glue, Redshift, Git, Snowflake, Databricks, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d4b101e186a751f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d850716a666a932</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI TEVV Engineer</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, Git, MySQL, NoSQL, Polars, Python, SQL</t>
+          <t>RAG, S3, Apache Airflow, Snowflake, Dask, Tableau, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
+          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior ML Engineer (Data Scientist)</t>
+          <t>Risk-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Dask, Python, SQL</t>
+          <t>RAG, S3, Apache Airflow, Snowflake, Dask, Tableau, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a680bbd22cb24e19</t>
+          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Consultant, AI/ML Ops Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>RAG, Gemini, S3, EC2, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04930b8a942f9b08</t>
+          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Consultant, AI/ML Engineer</t>
+          <t>Software Engineer, Cost Optimization (Infrastructure)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Kustomer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, XGBoost, S3, Docker, CI/CD, Terraform, Git</t>
+          <t>RAG, EC2, Kinesis, Terraform, Kafka, MongoDB, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cdedb23564fb186</t>
+          <t>https://www.indeed.com/viewjob?jk=b4265de86cf13137</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI &amp; Automation Intern (Summer 2027)</t>
+          <t>Data Analyst II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>Coventbridge Integrity Systems</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Matplotlib, Seaborn</t>
+          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af51cc5c563cfa8</t>
+          <t>https://www.indeed.com/viewjob?jk=4332cefe4e155d12</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Audience Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>PeopleConnect</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, Dataflow, Snowflake, Databricks, BigQuery, Tableau, Python, SQL</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbe4c00163046c9</t>
+          <t>https://www.indeed.com/viewjob?jk=eac4c63be1c1fa9b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dot NET / AI Engineer Full Stack Developer (AI-Assisted Development)</t>
+          <t>Platform Reliability Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avenel, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, SQL, R</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb467d33fe44bf6</t>
+          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Infrastructure Software Engineer, TensorRT Edge-LLM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, Dataflow, Snowflake, Databricks, BigQuery, Tableau, Python, SQL</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f044661c236d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c0bfc3dfc27486</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>AI Software Engineer - HP IQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, MLflow, CI/CD, Git, Databricks, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, TensorFlow, PyTorch, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
+          <t>https://www.indeed.com/viewjob?jk=614b7dd12b4b486c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Java Developer - Senior Software Engineer</t>
+          <t>Sr IAM Security Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>HealthEquity Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Python, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878c8798595a671b</t>
+          <t>https://www.indeed.com/viewjob?jk=34639969d758ae18</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kinesis, Git, Snowflake, Kafka, Python, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Java Developer - Senior Software Engineer</t>
+          <t>Senior Business Intelligence &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>County Materials Family of Companies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, R</t>
+          <t>AI Engineer, RAG, Synapse, Data Lake, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6121d23a371fe8d7</t>
+          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Snowflake, Kafka, SQL, R, Java</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
+          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Snowflake, Kafka, SQL, R, Java</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Snowflake, Kafka, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4a1f846bcacea7</t>
+          <t>https://www.indeed.com/viewjob?jk=c9f8797387532ab0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>F&amp;I Sentinel, LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Generative AI, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Copilot, FastAPI, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed508784ce002250</t>
+          <t>https://www.indeed.com/viewjob?jk=1df4c64b3bf863d3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>F&amp;I Sentinel, LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Data Scientist, Copilot, Git, Snowflake, Databricks, PySpark, Polars, Python, SQL, R</t>
+          <t>Copilot, FastAPI, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42cb9d30057bd56e</t>
+          <t>https://www.indeed.com/viewjob?jk=74905cebfc5007a8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>26-117: Fire Weather Testbed Cloud Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Colorado State University</t>
+          <t>F&amp;I Sentinel, LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, Terraform, Git, Python, R, Java</t>
+          <t>Copilot, FastAPI, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
+          <t>https://www.indeed.com/viewjob?jk=39fc58b7ed3d22b0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>F&amp;I Sentinel, LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Copilot, FastAPI, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
+          <t>https://www.indeed.com/viewjob?jk=45a214f5bcc1bae8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Product Owner</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jack Link's Protein Snacks</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Snowflake, Databricks, Power BI, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=e8503f888186c979</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Underwriting ML)</t>
+          <t>Data Scientist I - Quality Engineering (Electrophysiology)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Boston Scientific</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arden Hills, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, XGBoost, LightGBM, CatBoost, MLflow, Dask, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f89bf627dfff2c25</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5720e2ef6fbf12</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Architect (Solution Architect)</t>
+          <t>AI Marketing Analytics Specialist</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Burrow Global LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,672 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf7abecff1fad788</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Hudson Manpower</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=69ab1463c221cdc8</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>PODS</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Clearwater, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Data Scientist, Copilot, Git, Snowflake, Databricks, Python, SQL, R, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91af993731ab7949</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Senior Application Developer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>State of Indiana</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce169e58eb6bb198</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer I - Amex Ads, Offers, and Dining Technology</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>American Express</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Data Lake, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0e4c95a4a013032d</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Full stack</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Kafka, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f12ec47477543f16</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2878d7ff233cf040</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6fed3346e4ee25a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Sr. Java Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Intellibee Inc</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, Terraform, Git, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c658c9d4562b0e92</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=105926e91d839d32</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Founding AI Engineer</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>CLERA</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Hugging Face, PyTorch, Docker, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=955a600f5157a119</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>AI Validation Engineer</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Auburn Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, MLflow, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46ece8c5e66bc17b</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer I</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>AAA Washington</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, NoSQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d50322779edaaaaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2027 Data for Good Hackathon - Data &amp; AI Program - Summer Internship</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97e43de80f2f64a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Sr. Data Scientist, Data Scientist, Supply Chain Simulation and Fulfillment</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>The Home Depot</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f99a27c43ae9595</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Associate Data Scientist</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Sunbelt Rentals</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Fort Mill, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, Prompt Engineering, Docker, CI/CD, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5a40aa7f8f9335</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Software Engineer I - AI</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Chamberlain Group</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Oak Brook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a48a90ecea11ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Site Rel Eng III, GCP</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Optimum</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=503bb159bbcb48cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Site Rel Eng III, GCP</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Optimum</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Bethpage, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5eaa2a10cea951c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer- Backend</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, PyTorch, Azure ML, MLflow, Databricks, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=232a6e98b2cd1cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=35fc4b7105ed6a97</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-07.xlsx
+++ b/daily_matches/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Senior AI Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Ashra Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>35.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+          <t>AI Engineer, Data Scientist, Generative AI, Hugging Face, Prompt Engineering, Cortex, TensorFlow, PyTorch, XGBoost, LightGBM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7181c20be5b9947</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a696b44fd5d4a9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GLOBO</t>
+          <t>Ashra Technology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Storden, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Pinecone, Prompt Engineering, Snowflake, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Hugging Face, TensorFlow, PyTorch, XGBoost, LightGBM, CatBoost, AWS SageMaker, GCP Vertex AI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e967e02af93fb4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=82dfb61792cd2985</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Automation Engineer</t>
+          <t>Senior Java Microservices Developer (AI Experience) - W2 Only</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>EVOLVE SOLUTIONS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Snowflake, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, NoSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df85fe4b36a38ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=e58109447c5adc4a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Fullstack Python Software Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, FastAPI, CI/CD, Git, Python, SQL, R</t>
+          <t>RAG, Copilot, Glue, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fb40249f50f1729</t>
+          <t>https://www.indeed.com/viewjob?jk=a71fa5e470dbbd46</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PureMagic Carwash</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Docker, Terraform, Git, Snowflake, Power BI, Python, SQL</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,129 +636,129 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
+          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, S3, Glue, Apache Airflow, CI/CD, Databricks, PySpark, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
+          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Backend Python/Databricks Software Engineer III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, S3, Glue, Apache Airflow, CI/CD, Terraform, Databricks, PySpark, Kafka, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
+          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Senior Data Engineer (Python)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Hyundai AutoEver America</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Data Lake, Apache Airflow, CI/CD, Git, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
+          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (C++, AI/ML, OOP, Linux)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>Latham &amp; Watkins LLP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, Git, PostgreSQL, SQL, R, C++, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, LLaMA, TensorFlow, PyTorch, CI/CD, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beae57dae6d03453</t>
+          <t>https://www.indeed.com/viewjob?jk=46a67aa44c80b008</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, FastAPI, Docker, Kubernetes, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a58039548ce9d77</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbd0f1be61bb232</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>React Web Developer</t>
+          <t>Fullstack Python/AI Software Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, Git, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e02f10c7760289d</t>
+          <t>https://www.indeed.com/viewjob?jk=73c51cf9c12a9a15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Analytics and Research Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>Ookla</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Athena, Redshift, Git, Redshift, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2906710128d32d21</t>
+          <t>https://www.indeed.com/viewjob?jk=edd7a7609e26beb8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Decision Intelligence Engineer (NBA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Ookla</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,52 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, MLflow, Databricks, PySpark, Python, R, Optimization</t>
+          <t>Data Scientist, Athena, Redshift, Git, Redshift, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=155b500259c73df1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Machine Learning Scientist II - Pricing &amp; Economics</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Wayfair</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, XGBoost, MLflow, Docker, Kubernetes, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d29aa5cb1cd369bc</t>
+          <t>https://www.indeed.com/viewjob?jk=a76d47b947be4df2</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-07.xlsx
+++ b/daily_matches/job_matches_2026-08-07.xlsx
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer/Data Scientist</t>
+          <t>AI/ML Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ashra Technologies Pvt Ltd</t>
+          <t>Avilamb</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>35.6</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, Hugging Face, Prompt Engineering, Cortex, TensorFlow, PyTorch, XGBoost, LightGBM</t>
+          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, MLflow, Kubernetes, AKS, CI/CD, Databricks, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a696b44fd5d4a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>System Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ashra Technology</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Storden, MN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Hugging Face, TensorFlow, PyTorch, XGBoost, LightGBM, CatBoost, AWS SageMaker, GCP Vertex AI</t>
+          <t>Docker, Kubernetes, Git, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82dfb61792cd2985</t>
+          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Java Microservices Developer (AI Experience) - W2 Only</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EVOLVE SOLUTIONS</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, NoSQL, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,119 +566,119 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58109447c5adc4a</t>
+          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fullstack Python Software Engineer III</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a71fa5e470dbbd46</t>
+          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+          <t>Copilot, Docker, CI/CD, Git, Snowflake, Databricks, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Daniel Island, SC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Apache Airflow, CI/CD, Databricks, PySpark, Kafka, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
+          <t>https://www.indeed.com/viewjob?jk=8b8b86f05642ffe9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Backend Python/Databricks Software Engineer III</t>
+          <t>Software Engineer III - Python/AWS/AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,15 +688,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Apache Airflow, CI/CD, Terraform, Databricks, PySpark, Kafka, Python</t>
+          <t>Data Scientist, RAG, S3, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
+          <t>https://www.indeed.com/viewjob?jk=27a62cd1a8dbfd15</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Agentic AI Intern (Paid Internship)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>CustomerInsights.AI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, PostgreSQL, Python, SQL</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, AWS SageMaker, Azure ML, Athena, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
+          <t>https://www.indeed.com/viewjob?jk=50e9e67dbd7cf251</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python)</t>
+          <t>Senior Mobile Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hyundai AutoEver America</t>
+          <t>WISEcode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Apache Airflow, CI/CD, Git, PySpark, Python, SQL, R</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
+          <t>https://www.indeed.com/viewjob?jk=4012f1b40056d555</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Site Reliability Engineer (SRE) (Hybrid)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Latham &amp; Watkins LLP</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, LLaMA, TensorFlow, PyTorch, CI/CD, Python, R, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a67aa44c80b008</t>
+          <t>https://www.indeed.com/viewjob?jk=4c32694bdf7bfcda</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer ILS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>NFI Industries</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, FastAPI, Docker, Kubernetes, Python, R, Scala</t>
+          <t>RAG, LLaMA, Kubernetes, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbd0f1be61bb232</t>
+          <t>https://www.indeed.com/viewjob?jk=d9d4f83115f86c43</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fullstack Python/AI Software Engineer III</t>
+          <t>Senior Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c51cf9c12a9a15</t>
+          <t>https://www.indeed.com/viewjob?jk=e1cff779082af95f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ookla</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Athena, Redshift, Git, Redshift, MySQL, Python, SQL, R</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edd7a7609e26beb8</t>
+          <t>https://www.indeed.com/viewjob?jk=68bb22b1d1a8ac4e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Business Intelligence Data Analyst - Torrance, CA - 2381326</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ookla</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Athena, Redshift, Git, Redshift, MySQL, Python, SQL, R</t>
+          <t>RAG, Redshift, Snowflake, Databricks, Redshift, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a76d47b947be4df2</t>
+          <t>https://www.indeed.com/viewjob?jk=8d745330722364ba</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-07.xlsx
+++ b/daily_matches/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Architect</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Avilamb</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, MLflow, Kubernetes, AKS, CI/CD, Databricks, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,137 +496,137 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>System Software Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Git, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
+          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate IE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>MasonHub</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fontana, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Git, Snowflake, Databricks, Kafka, Python, SQL, R</t>
+          <t>RAG, BigQuery, Snowflake, BigQuery, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
+          <t>https://www.indeed.com/viewjob?jk=29b0c1d327a76dec</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>AI Engineer – LLM / MCP / RAG / Agentic AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VGMT GLOBAL IT SOLUTIONS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Daniel Island, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b8b86f05642ffe9</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe27760a2b57093</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/AWS/AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Colorado Rockies Baseball Club</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala</t>
+          <t>RAG, Data Lake, Apache Airflow, Terraform, Snowflake, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a62cd1a8dbfd15</t>
+          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Agentic AI Intern (Paid Internship)</t>
+          <t>Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CustomerInsights.AI</t>
+          <t>MyFitnessPal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, AWS SageMaker, Azure ML, Athena, Python, SQL, R</t>
+          <t>Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e9e67dbd7cf251</t>
+          <t>https://www.indeed.com/viewjob?jk=211da0d53cbd0e9f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Mobile Developer</t>
+          <t>Software Engineer II – AI Agents &amp; Harnesses</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WISEcode</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4012f1b40056d555</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c9ed72758cf2a3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE) (Hybrid)</t>
+          <t>FULL STACK AI ENGINEER (SENIOR)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Ant-Tech</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c32694bdf7bfcda</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3ebfa39b0636e2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ILS</t>
+          <t>Sr Software Engineer - AI Lab, Ag &amp; Trading North America</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NFI Industries</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Wayzata, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Kubernetes, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,112 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9d4f83115f86c43</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1cff779082af95f</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68bb22b1d1a8ac4e</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Business Intelligence Data Analyst - Torrance, CA - 2381326</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Torrance, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Snowflake, Databricks, Redshift, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d745330722364ba</t>
+          <t>https://www.indeed.com/viewjob?jk=cf6bbab21117fdcc</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-07.xlsx
+++ b/daily_matches/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Consulting Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, TensorFlow, Keras, Docker, Kubernetes, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Specialty AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
+          <t>https://www.indeed.com/viewjob?jk=b8dba962461ec5c8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Specialty AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=89c09c3ad515600c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Data Engineer — GCP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
+          <t>RAG, Gemini, BigQuery, Dataflow, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
+          <t>https://www.indeed.com/viewjob?jk=5f84280e7ee9940e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate IE</t>
+          <t>Data Scientist III - Fraud Analytics &amp; Machine Learning</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MasonHub</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fontana, CA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Snowflake, BigQuery, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, BigQuery, Git, BigQuery, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b0c1d327a76dec</t>
+          <t>https://www.indeed.com/viewjob?jk=77b7fccbf5c17638</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer – LLM / MCP / RAG / Agentic AI</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VGMT GLOBAL IT SOLUTIONS</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java</t>
+          <t>Machine Learning Engineer, RAG, AWS SageMaker, GCP Vertex AI, Azure ML, Docker, Kubernetes, AKS, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe27760a2b57093</t>
+          <t>https://www.indeed.com/viewjob?jk=b22e167e69bdfe92</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Architect 2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Colorado Rockies Baseball Club</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Apache Airflow, Terraform, Snowflake, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, AWS SageMaker, GCP Vertex AI, Azure ML, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
+          <t>https://www.indeed.com/viewjob?jk=08d5fa709c2abfb2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>Machine Learning Architect 2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MyFitnessPal</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, AWS SageMaker, GCP Vertex AI, Azure ML, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211da0d53cbd0e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=d2689a7adb5339b8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer II – AI Agents &amp; Harnesses</t>
+          <t>Data Analyst FP&amp;A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Benjamin Moore</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Snowflake, PySpark, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c9ed72758cf2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=7fbdcd37317ac0a1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FULL STACK AI ENGINEER (SENIOR)</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ant-Tech</t>
+          <t>Fusion Global Solutions LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, FastAPI, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,42 +811,567 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3ebfa39b0636e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e38c607b1a35b2ad</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI Lab, Ag &amp; Trading North America</t>
+          <t>Senior Full Stack Python Developer - Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Tech Interacts Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>S3, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Architect</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Azure ML, Synapse, Git, Databricks, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49d09dd3954860f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Architect</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Azure ML, Synapse, Git, Databricks, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39e748263f2effdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Architect</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Azure ML, Synapse, Git, Databricks, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68194f35870b68d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Intelligent Automation &amp; AI Orchestration</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63ffe8ee3ad34901</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Eningeer(Mid-level, Senior)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9808bf5b941ca91</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TeamViewer</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7dffcff7eaaa7414</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc6cd92b9bfb7928</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI Architect (Agentic AI, ADK, Vertex)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>11.1</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf6bbab21117fdcc</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, BigQuery, Dataflow, Kubernetes, CI/CD, BigQuery, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e0b1d80dce70748</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Billtrust</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Git, MySQL, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Scientist, NA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Vantage Data Centers</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6e1eb03b9159fc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI Software Developer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TrueNorth</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Guaynabo, PR, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Mistral, Pinecone, Prompt Engineering, CI/CD, Python, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=234ae57ac00a8ed0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Junior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Git, Python, SQL, R, Optimization, Bayesian, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1b8fccc1a0c6451</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Git, Python, SQL, R, Optimization, Bayesian, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6eb240ab33c7406c</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Scientist - Delivery Data Science</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=208f709bfefc115a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-07.xlsx
+++ b/daily_matches/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consulting Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, TensorFlow, Keras, Docker, Kubernetes, Git, Snowflake</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
+          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Specialty AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Glue, Redshift, Data Lake, Kinesis, Git, Snowflake, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8dba962461ec5c8</t>
+          <t>https://www.indeed.com/viewjob?jk=1c780bb7cb6c4cc0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Specialty AI Engineer</t>
+          <t>Python Backend Developer - Hybrid/Onsite</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c09c3ad515600c</t>
+          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — GCP</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Salvo Software</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Gemini, BigQuery, Dataflow, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
+          <t>Machine Learning Engineer, RAG, LLaMA, Mistral, Hugging Face, FAISS, TensorFlow, PyTorch, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f84280e7ee9940e</t>
+          <t>https://www.indeed.com/viewjob?jk=9fef5eff14723a94</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist III - Fraud Analytics &amp; Machine Learning</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, BigQuery, Git, BigQuery, Tableau, Power BI</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, S3, Docker</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b7fccbf5c17638</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c803152f342224</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, AWS SageMaker, GCP Vertex AI, Azure ML, Docker, Kubernetes, AKS, CI/CD, GitHub Actions</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b22e167e69bdfe92</t>
+          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Architect 2</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, AWS SageMaker, GCP Vertex AI, Azure ML, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git</t>
+          <t>LangChain, RAG, LLaMA, S3, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d5fa709c2abfb2</t>
+          <t>https://www.indeed.com/viewjob?jk=033a483ab033f139</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Architect 2</t>
+          <t>Senior Solution Architect - I&amp;D</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Franklin Lakes, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, AWS SageMaker, GCP Vertex AI, Azure ML, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git</t>
+          <t>RAG, Glue, Data Lake, Snowflake, Databricks, Kafka, Hadoop, NoSQL, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2689a7adb5339b8</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed54c8ce6b401fd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Analyst FP&amp;A</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Benjamin Moore</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Snowflake, PySpark, Tableau, Power BI</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Git, Kafka, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fbdcd37317ac0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GenAI Engineer</t>
+          <t>GenAI GenOS Engineer (Senior)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fusion Global Solutions LLC</t>
+          <t>Bintech Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, FastAPI, Hadoop, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Mistral, Pinecone, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e38c607b1a35b2ad</t>
+          <t>https://www.indeed.com/viewjob?jk=2fff9243547767e9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack Python Developer - Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tech Interacts Inc</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Des Plaines, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S3, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Git, Databricks, Hadoop, MongoDB, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
+          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Architect</t>
+          <t>AI/ML Engineer Precision Oncology</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Azure ML, Synapse, Git, Databricks, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Hugging Face, PyTorch, Docker, Git, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49d09dd3954860f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7108e16cc040c67d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Architect</t>
+          <t>AI/ML Engineer Precision Oncology</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Azure ML, Synapse, Git, Databricks, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Hugging Face, PyTorch, Docker, Git, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e748263f2effdc</t>
+          <t>https://www.indeed.com/viewjob?jk=43a1dd1473a6d493</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Architect</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Burford Capital</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Azure ML, Synapse, Git, Databricks, Python, SQL, R, Optimization</t>
+          <t>Generative AI, RAG, Docker, CI/CD, GitHub Actions, Git, Snowflake, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68194f35870b68d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c48ae6a363826aa7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Machine Learning Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Azure ML, Synapse, Git, Databricks, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
+          <t>https://www.indeed.com/viewjob?jk=3ddcec0f10bc756c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Intelligent Automation &amp; AI Orchestration</t>
+          <t>Senior Machine Learning Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
+          <t>Data Scientist, RAG, Azure ML, Synapse, Git, Databricks, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63ffe8ee3ad34901</t>
+          <t>https://www.indeed.com/viewjob?jk=82f1a16d9f2d28bb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Eningeer(Mid-level, Senior)</t>
+          <t>Software Engineer, Digital Workplace</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Prompt Engineering, GCP Vertex AI, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9808bf5b941ca91</t>
+          <t>https://www.indeed.com/viewjob?jk=380d411df5f1bd35</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Scientist (Internal Audit Model &amp; AI Risk)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TeamViewer</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, AKS, Databricks, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dffcff7eaaa7414</t>
+          <t>https://www.indeed.com/viewjob?jk=f8607c4826116c11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6cd92b9bfb7928</t>
+          <t>https://www.indeed.com/viewjob?jk=0da9fa927be823d4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Architect (Agentic AI, ADK, Vertex)</t>
+          <t>Software Systems Engineer II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Makpar Corporation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Gemini, BigQuery, Dataflow, Kubernetes, CI/CD, BigQuery, Python, R, Java</t>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e0b1d80dce70748</t>
+          <t>https://www.indeed.com/viewjob?jk=35b547c123699471</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Data Scientist Precision Oncology</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Git, MySQL, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Git, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=841a59387c76efe8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist, NA</t>
+          <t>AI Data Scientist Precision Oncology</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Git, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e1eb03b9159fc6</t>
+          <t>https://www.indeed.com/viewjob?jk=b55ebb56d14c5fc5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Software Developer</t>
+          <t>Senior Knowledge Graph Data Engineer - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TrueNorth</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Mistral, Pinecone, Prompt Engineering, CI/CD, Python, R</t>
+          <t>Generative AI, RAG, Docker, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,19 +1266,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234ae57ac00a8ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=5db9cfaf2bc485b1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Junior Machine Learning Engineer</t>
+          <t>Knowledge Graph Data Engineer – QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Git, Python, SQL, R, Optimization, Bayesian, Hypothesis Testing</t>
+          <t>Generative AI, RAG, Docker, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1b8fccc1a0c6451</t>
+          <t>https://www.indeed.com/viewjob?jk=a1324b3bdb9e9296</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Junior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb240ab33c7406c</t>
+          <t>https://www.indeed.com/viewjob?jk=6bd7458abe51f5f4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Scientist - Delivery Data Science</t>
+          <t>Software Engineer V, Forward Deployed</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>X-Energy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,262 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>LangChain, RAG, Docker, CI/CD, Terraform, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d57a8151bad101b</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>React Web Developer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, S3, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91c6b4cd501bf74f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Quality Engineer - Hybrid On-Site</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Merrimack, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Oracle Data Engineer - Onsite</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Oracle Data Engineer - Onsite</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist - Network Strategy</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=208f709bfefc115a</t>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=583feac1cd902526</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Scientist, Firefly</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71d04d8255a296c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Security Engineer - McKinsey ID</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>McKinsey &amp; Company</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdd0eb4272b60468</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-07.xlsx
+++ b/daily_matches/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Technical Architect 8</t>
+          <t>Software Engineer II-Hybrid Role</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Mistral, Prompt Engineering, Azure ML, Redshift</t>
+          <t>TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, MySQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Azure DBX</t>
+          <t>Quality Engineer (AI Automation)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark</t>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8699eca260e46b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=d81d35ca5c6c5d71</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cactus Wellhead - Sr. Data Platform Engineering</t>
+          <t>Quality Engineer (AI Automation)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cactus Wellhead</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Git, Databricks, PySpark, PostgreSQL, Tableau, Power BI, Python</t>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33763b20c7bc7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=b7a3a413446d2ca7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java Kafka Software Engineer III</t>
+          <t>Quality Engineer (AI Automation)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8f8a43248b5c38</t>
+          <t>https://www.indeed.com/viewjob?jk=ef82f2b8de2b6c8d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Quality Engineer (AI &amp; Test Automation)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Magid Glove &amp; Safety</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romeoville, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, CI/CD, Git, Snowflake, Databricks, BigQuery, Power BI, Python</t>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=2188a2e1704e2a15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer with AI</t>
+          <t>Quality Engineer (AI Automation)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, R, Java, Scala</t>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cc4d36ef15bab82</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd6783edec6917f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Analyst/Engineer</t>
+          <t>Quality Engineer (AI &amp; Test Automation)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Data Lake, Git, Snowflake, Tableau, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,462 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5e6ad9d3fe6b85</t>
+          <t>https://www.indeed.com/viewjob?jk=ef8cf36937702de4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate - Software Development &amp; Engineering</t>
+          <t>Quality Engineer (AI Automation)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=866684bb39c7d1e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Quality Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=433e7f4566f574ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Quality Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>El Dorado Hills, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6e4b852c27e8d06</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Quality Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c456957864559308</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Quality Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c16c0e945e955e1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Quality Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D14" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af4bd4c6bf1078e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Quality Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7a7ae1c10efc2dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Quality Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce253d168d710d6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Quality Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=562e2bfb7b81e103</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Quality Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5df6ed5e6c99af2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Machine Learning Architect II</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, AWS SageMaker, GCP Vertex AI, Azure ML, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3baaefe539df3d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Cloud Platform</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb7591d99652fd20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer / Developer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Digital Harbor</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Lehi, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6541c887ab15b56c</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, CI/CD, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c45c942ab6d16d30</t>
         </is>
       </c>
     </row>
